--- a/data/test_data_swing_mobile.xlsx
+++ b/data/test_data_swing_mobile.xlsx
@@ -1,428 +1,629 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView windowHeight="16360" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Driving_Range" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Tee_Time" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Tee_Time_Player" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Driving_Range" sheetId="1" r:id="rId1"/>
+    <sheet name="Tee_Time" sheetId="2" r:id="rId2"/>
+    <sheet name="Tee_Time_Player" sheetId="3" r:id="rId3"/>
+    <sheet name="Events" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="120">
-  <si>
-    <t xml:space="preserve">ACTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRIVING_RANGE_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOOKING_DATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAY_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIME_SLOT_START</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIME_SLOT_END</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUMBER_OF_BAYS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDON_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDON_QTY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMO_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMO_CODE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAYMENT_METHOD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESCHEDULE_DAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESCHEDULE_TIME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESCHEDULE_REASON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCEL_REASON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANK_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANK_ACCOUNT_NUMBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANK_ACCOUNT_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_DR_00001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal Booking Driving Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indonesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albatross Driving Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rental stick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_DR_00002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Booking With Promo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[TESTING] DR11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_DR_00003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Booking With Auto-Applied Promo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_DR_00004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Booking Without Promo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_DR_00005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reschedule Booking Driving Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bad weather</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_DR_00006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancel Booking Driving Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPD Bali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRRR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEARCH_QUERY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COURSE_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALENDAR_DATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREFERRED_TIME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOST_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOST_PROMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXPECTED_RESULT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TT_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book Standard Tee Time - Full E2E (3 players)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rainbow Hills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rainbow Hills Golf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:30 - 10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Auto Mation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Testing] Automation Tee time Promo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWING123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booking paid successfully with 3 players and host promo applied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TT_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Payment - With Promo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:30 - 09:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promo applied to host, payment method set to VISA 0014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TT_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Payment - Without Promo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-applied promo removed from host, payment method set to VISA 0014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TT_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Book Tee Time - Full 4 Players (e-wallet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:00 - 09:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booking paid successfully with host + 3 invitees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAYER_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METHOD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIRST_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAST_NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMAIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andi Wijaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wijaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81234567890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">andi.wijaya@example.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tam Lembong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budi Santoso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santoso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81299887766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">budi.santoso@example.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citra Dewi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dewi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81355501122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">citra.dewi@example.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dian Pratama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pratama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81366602233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dian.pratama@example.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eka Kurniawan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurniawan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81377703344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eka.kurniawan@example.com</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="137">
+  <si>
+    <t>ACTION</t>
+  </si>
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>TC_NAME</t>
+  </si>
+  <si>
+    <t>REGION</t>
+  </si>
+  <si>
+    <t>DRIVING_RANGE_NAME</t>
+  </si>
+  <si>
+    <t>BOOKING_DATE</t>
+  </si>
+  <si>
+    <t>BAY_NAME</t>
+  </si>
+  <si>
+    <t>TIME_SLOT_START</t>
+  </si>
+  <si>
+    <t>TIME_SLOT_END</t>
+  </si>
+  <si>
+    <t>NUMBER_OF_BAYS</t>
+  </si>
+  <si>
+    <t>ADDON_NAME</t>
+  </si>
+  <si>
+    <t>ADDON_QTY</t>
+  </si>
+  <si>
+    <t>PROMO_NAME</t>
+  </si>
+  <si>
+    <t>PROMO_CODE</t>
+  </si>
+  <si>
+    <t>PAYMENT_METHOD</t>
+  </si>
+  <si>
+    <t>RESCHEDULE_DAY</t>
+  </si>
+  <si>
+    <t>RESCHEDULE_TIME</t>
+  </si>
+  <si>
+    <t>RESCHEDULE_REASON</t>
+  </si>
+  <si>
+    <t>CANCEL_REASON</t>
+  </si>
+  <si>
+    <t>BANK_NAME</t>
+  </si>
+  <si>
+    <t>BANK_ACCOUNT_NUMBER</t>
+  </si>
+  <si>
+    <t>BANK_ACCOUNT_NAME</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>TC_DR_00001</t>
+  </si>
+  <si>
+    <t>Normal Booking Driving Range</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Albatross Driving Range</t>
+  </si>
+  <si>
+    <t>08 August 2026</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>Rental stick</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>OVO</t>
+  </si>
+  <si>
+    <t>TC_DR_00002</t>
+  </si>
+  <si>
+    <t>E2E Booking With Promo</t>
+  </si>
+  <si>
+    <t>10 August 2026</t>
+  </si>
+  <si>
+    <t>[TESTING] DR11</t>
+  </si>
+  <si>
+    <t>TC_DR_00003</t>
+  </si>
+  <si>
+    <t>E2E Booking With Auto-Applied Promo</t>
+  </si>
+  <si>
+    <t>11 August 2026</t>
+  </si>
+  <si>
+    <t>TC_DR_00004</t>
+  </si>
+  <si>
+    <t>E2E Booking Without Promo</t>
+  </si>
+  <si>
+    <t>13 August 2026</t>
+  </si>
+  <si>
+    <t>TC_DR_00005</t>
+  </si>
+  <si>
+    <t>Reschedule Booking Driving Range</t>
+  </si>
+  <si>
+    <t>18 August 2026</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>Bad weather</t>
+  </si>
+  <si>
+    <t>TC_DR_00006</t>
+  </si>
+  <si>
+    <t>Cancel Booking Driving Range</t>
+  </si>
+  <si>
+    <t>BPD Bali</t>
+  </si>
+  <si>
+    <t>SRRR</t>
+  </si>
+  <si>
+    <t>SEARCH_QUERY</t>
+  </si>
+  <si>
+    <t>COURSE_NAME</t>
+  </si>
+  <si>
+    <t>CALENDAR_DATE</t>
+  </si>
+  <si>
+    <t>PREFERRED_TIME</t>
+  </si>
+  <si>
+    <t>HOST_NAME</t>
+  </si>
+  <si>
+    <t>HOST_PROMO</t>
+  </si>
+  <si>
+    <t>EXPECTED_RESULT</t>
+  </si>
+  <si>
+    <t>TT_001</t>
+  </si>
+  <si>
+    <t>Book Standard Tee Time - Full E2E (3 players)</t>
+  </si>
+  <si>
+    <t>Rainbow Hills</t>
+  </si>
+  <si>
+    <t>Rainbow Hills Golf</t>
+  </si>
+  <si>
+    <t>19 August 2026</t>
+  </si>
+  <si>
+    <t>09:30 - 10:00</t>
+  </si>
+  <si>
+    <t>QA Auto Mation</t>
+  </si>
+  <si>
+    <t>[Testing] Automation Tee time Promo</t>
+  </si>
+  <si>
+    <t>SWING123</t>
+  </si>
+  <si>
+    <t>Booking paid successfully with 3 players and host promo applied</t>
+  </si>
+  <si>
+    <t>TT_002</t>
+  </si>
+  <si>
+    <t>Select Payment - With Promo</t>
+  </si>
+  <si>
+    <t>02 August 2026</t>
+  </si>
+  <si>
+    <t>08:30 - 09:00</t>
+  </si>
+  <si>
+    <t>Promo applied to host, payment method set to VISA 0014</t>
+  </si>
+  <si>
+    <t>TT_003</t>
+  </si>
+  <si>
+    <t>Select Payment - Without Promo</t>
+  </si>
+  <si>
+    <t>03 August 2026</t>
+  </si>
+  <si>
+    <t>Auto-applied promo removed from host, payment method set to VISA 0014</t>
+  </si>
+  <si>
+    <t>TT_004</t>
+  </si>
+  <si>
+    <t>Book Tee Time - Full 4 Players (e-wallet)</t>
+  </si>
+  <si>
+    <t>05 August 2026</t>
+  </si>
+  <si>
+    <t>09:00 - 09:30</t>
+  </si>
+  <si>
+    <t>Booking paid successfully with host + 3 invitees</t>
+  </si>
+  <si>
+    <t>PLAYER_NAME</t>
+  </si>
+  <si>
+    <t>METHOD</t>
+  </si>
+  <si>
+    <t>FIRST_NAME</t>
+  </si>
+  <si>
+    <t>LAST_NAME</t>
+  </si>
+  <si>
+    <t>PHONE</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>PROMO</t>
+  </si>
+  <si>
+    <t>Andi Wijaya</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>Andi</t>
+  </si>
+  <si>
+    <t>Wijaya</t>
+  </si>
+  <si>
+    <t>81234567890</t>
+  </si>
+  <si>
+    <t>andi.wijaya@example.com</t>
+  </si>
+  <si>
+    <t>Tam Lembong</t>
+  </si>
+  <si>
+    <t>search</t>
+  </si>
+  <si>
+    <t>Budi Santoso</t>
+  </si>
+  <si>
+    <t>Budi</t>
+  </si>
+  <si>
+    <t>Santoso</t>
+  </si>
+  <si>
+    <t>81299887766</t>
+  </si>
+  <si>
+    <t>budi.santoso@example.com</t>
+  </si>
+  <si>
+    <t>Citra Dewi</t>
+  </si>
+  <si>
+    <t>Citra</t>
+  </si>
+  <si>
+    <t>Dewi</t>
+  </si>
+  <si>
+    <t>81355501122</t>
+  </si>
+  <si>
+    <t>citra.dewi@example.com</t>
+  </si>
+  <si>
+    <t>Dian Pratama</t>
+  </si>
+  <si>
+    <t>Dian</t>
+  </si>
+  <si>
+    <t>Pratama</t>
+  </si>
+  <si>
+    <t>81366602233</t>
+  </si>
+  <si>
+    <t>dian.pratama@example.com</t>
+  </si>
+  <si>
+    <t>Eka Kurniawan</t>
+  </si>
+  <si>
+    <t>Eka</t>
+  </si>
+  <si>
+    <t>Kurniawan</t>
+  </si>
+  <si>
+    <t>81377703344</t>
+  </si>
+  <si>
+    <t>eka.kurniawan@example.com</t>
+  </si>
+  <si>
+    <t>EVENT_NAME</t>
+  </si>
+  <si>
+    <t>BOOKING_TYPE</t>
+  </si>
+  <si>
+    <t>REGISTRATION_TIME</t>
+  </si>
+  <si>
+    <t>TC_E_001</t>
+  </si>
+  <si>
+    <t>Closed Registration Booking</t>
+  </si>
+  <si>
+    <t>Tournament Best Ball</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>TC_E_002</t>
+  </si>
+  <si>
+    <t>Standard Registration Booking</t>
+  </si>
+  <si>
+    <t>TEST Scanner</t>
+  </si>
+  <si>
+    <t>Standard registration</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>@cindyy</t>
+  </si>
+  <si>
+    <t>TC_E_003</t>
+  </si>
+  <si>
+    <t>Group Registration Booking</t>
+  </si>
+  <si>
+    <t>Group registration</t>
+  </si>
+  <si>
+    <t>Joko</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -435,184 +636,843 @@
         <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="9">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF305496"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00305496"/>
+      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -662,37 +1522,36 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V7"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5357142857143" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="6"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="13.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="18.94"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="17.32"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="18" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="24" style="1" width="11.53"/>
+    <col min="1" max="2" width="13.6071428571429" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.4285714285714" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.8839285714286" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5535714285714" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6428571428571" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.2410714285714" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3392857142857" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.2410714285714" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5357142857143" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.1428571428571" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6339285714286" style="1" customWidth="1"/>
+    <col min="13" max="14" width="14.4285714285714" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.9375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5267857142857" style="1"/>
+    <col min="17" max="17" width="17.3214285714286" style="1" customWidth="1"/>
+    <col min="18" max="22" width="11.5267857142857" style="1"/>
+    <col min="24" max="16384" width="11.5267857142857" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="33" customHeight="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,7 +1619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="44.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="44.25" customHeight="1" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -788,7 +1647,7 @@
       <c r="I2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="1">
         <v>3</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -801,7 +1660,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="22.5" customHeight="1" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -829,13 +1688,13 @@
       <c r="I3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="1">
         <v>3</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3" s="1">
         <v>2</v>
       </c>
       <c r="M3" s="1" t="s">
@@ -845,7 +1704,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="43" customHeight="1" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -873,13 +1732,13 @@
       <c r="I4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="1">
         <v>3</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="1">
         <v>2</v>
       </c>
       <c r="M4" s="1" t="s">
@@ -889,7 +1748,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="22.5" customHeight="1" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -917,13 +1776,13 @@
       <c r="I5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="1">
         <v>3</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="1">
         <v>2</v>
       </c>
       <c r="M5" s="1" t="s">
@@ -933,7 +1792,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="22.5" customHeight="1" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -974,7 +1833,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="22.5" customHeight="1" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -1011,7 +1870,7 @@
       <c r="T7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="U7" s="1">
         <v>12354</v>
       </c>
       <c r="V7" s="1" t="s">
@@ -1019,10 +1878,9 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
@@ -1030,27 +1888,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.48828125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.49107142857143" defaultRowHeight="15" customHeight="1" outlineLevelRow="4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="2" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="2" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="42"/>
+    <col min="1" max="2" width="10" style="2" customWidth="1"/>
+    <col min="3" max="3" width="42" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20" style="2" customWidth="1"/>
+    <col min="7" max="9" width="16" style="2" customWidth="1"/>
+    <col min="10" max="10" width="37" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16" style="2" customWidth="1"/>
+    <col min="12" max="12" width="37" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12" style="2" customWidth="1"/>
+    <col min="14" max="14" width="42" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customHeight="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1094,7 +1950,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1138,7 +1994,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1182,7 +2038,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customHeight="1" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1217,7 +2073,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customHeight="1" spans="1:14">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -1262,36 +2118,30 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="8.48828125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.49107142857143" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="37"/>
+    <col min="1" max="1" width="10" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13" style="2" customWidth="1"/>
+    <col min="7" max="7" width="27" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13" style="2" customWidth="1"/>
+    <col min="9" max="9" width="37" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -1320,7 +2170,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customHeight="1" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>60</v>
       </c>
@@ -1343,7 +2193,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customHeight="1" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>60</v>
       </c>
@@ -1360,7 +2210,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>60</v>
       </c>
@@ -1383,7 +2233,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>70</v>
       </c>
@@ -1409,7 +2259,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customHeight="1" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>75</v>
       </c>
@@ -1432,7 +2282,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customHeight="1" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>79</v>
       </c>
@@ -1455,7 +2305,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customHeight="1" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>79</v>
       </c>
@@ -1472,7 +2322,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customHeight="1" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>79</v>
       </c>
@@ -1496,12 +2346,124 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="7"/>
+  <cols>
+    <col min="2" max="2" width="12.1964285714286" customWidth="1"/>
+    <col min="3" max="3" width="26.1875" customWidth="1"/>
+    <col min="4" max="4" width="28.125" customWidth="1"/>
+    <col min="5" max="5" width="19.7857142857143" customWidth="1"/>
+    <col min="6" max="6" width="20.2321428571429" customWidth="1"/>
+    <col min="7" max="7" width="29.0178571428571" customWidth="1"/>
+    <col min="8" max="8" width="20.3839285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/data/test_data_swing_mobile.xlsx
+++ b/data/test_data_swing_mobile.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16360" tabRatio="500" activeTab="3"/>
+    <workbookView windowHeight="17160" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Driving_Range" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="147">
   <si>
     <t>ACTION</t>
   </si>
@@ -401,6 +401,9 @@
     <t>REGISTRATION_TIME</t>
   </si>
   <si>
+    <t>SWITCH_REGISTRATION_TYPE</t>
+  </si>
+  <si>
     <t>TC_E_001</t>
   </si>
   <si>
@@ -441,6 +444,33 @@
   </si>
   <si>
     <t>Joko</t>
+  </si>
+  <si>
+    <t>TC_E_004</t>
+  </si>
+  <si>
+    <t>Swith from Standard to Group Registration Booking</t>
+  </si>
+  <si>
+    <t>Tournament AIGG Test</t>
+  </si>
+  <si>
+    <t>TC_E_005</t>
+  </si>
+  <si>
+    <t>Swith from Group to Standard Registration Booking</t>
+  </si>
+  <si>
+    <t>TC_E_006</t>
+  </si>
+  <si>
+    <t>Keep player case</t>
+  </si>
+  <si>
+    <t>TC_E_007</t>
+  </si>
+  <si>
+    <t>Remove player case</t>
   </si>
 </sst>
 </file>
@@ -2355,19 +2385,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="12.1964285714286" customWidth="1"/>
-    <col min="3" max="3" width="26.1875" customWidth="1"/>
+    <col min="3" max="3" width="48.0625" customWidth="1"/>
     <col min="4" max="4" width="28.125" customWidth="1"/>
     <col min="5" max="5" width="19.7857142857143" customWidth="1"/>
     <col min="6" max="6" width="20.2321428571429" customWidth="1"/>
     <col min="7" max="7" width="29.0178571428571" customWidth="1"/>
     <col min="8" max="8" width="20.3839285714286" customWidth="1"/>
+    <col min="9" max="9" width="30.9285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:8">
+    <row r="1" ht="15" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2392,74 +2423,181 @@
       <c r="H1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H4" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/data/test_data_swing_mobile.xlsx
+++ b/data/test_data_swing_mobile.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17160" tabRatio="500" activeTab="3"/>
+    <workbookView windowHeight="17160" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Driving_Range" sheetId="1" r:id="rId1"/>
     <sheet name="Tee_Time" sheetId="2" r:id="rId2"/>
     <sheet name="Tee_Time_Player" sheetId="3" r:id="rId3"/>
     <sheet name="Events" sheetId="4" r:id="rId4"/>
+    <sheet name="Multisport" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="170">
   <si>
     <t>ACTION</t>
   </si>
@@ -471,6 +472,75 @@
   </si>
   <si>
     <t>Remove player case</t>
+  </si>
+  <si>
+    <t>SPORT_NAME</t>
+  </si>
+  <si>
+    <t>VENUE_NAME</t>
+  </si>
+  <si>
+    <t>TITLE_SCHEDULE</t>
+  </si>
+  <si>
+    <t>HOW_MUCH_SCHEDULE</t>
+  </si>
+  <si>
+    <t>TC_MLTS_001</t>
+  </si>
+  <si>
+    <t>Verify user can choose sport from sport option page</t>
+  </si>
+  <si>
+    <t>BILLIARD</t>
+  </si>
+  <si>
+    <t>TC_MLTS_002</t>
+  </si>
+  <si>
+    <t>Verify user can choose venue</t>
+  </si>
+  <si>
+    <t>BillWithPPD</t>
+  </si>
+  <si>
+    <t>TC_MLTS_003</t>
+  </si>
+  <si>
+    <t>Verify user can book venue</t>
+  </si>
+  <si>
+    <t>TC_MLTS_004</t>
+  </si>
+  <si>
+    <t>Verify user can select schedule</t>
+  </si>
+  <si>
+    <t>table1</t>
+  </si>
+  <si>
+    <t>TC_MLTS_005</t>
+  </si>
+  <si>
+    <t>Verify user can select add player</t>
+  </si>
+  <si>
+    <t>TC_MLTS_006</t>
+  </si>
+  <si>
+    <t>Verify user can remove player</t>
+  </si>
+  <si>
+    <t>TC_MLTS_007</t>
+  </si>
+  <si>
+    <t>Verify user can select payment</t>
+  </si>
+  <si>
+    <t>TC_MLTS_008</t>
+  </si>
+  <si>
+    <t>Verify user can book venue end to end until payment</t>
   </si>
 </sst>
 </file>
@@ -2604,4 +2674,205 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="30.2053571428571" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="30.2053571428571" customWidth="1"/>
+    <col min="2" max="2" width="45.375" customWidth="1"/>
+    <col min="3" max="3" width="41.0714285714286" customWidth="1"/>
+    <col min="4" max="16384" width="30.2053571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:8">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/data/test_data_swing_mobile.xlsx
+++ b/data/test_data_swing_mobile.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17160" tabRatio="500" firstSheet="4" activeTab="9"/>
+    <workbookView windowHeight="16360" tabRatio="500" firstSheet="4" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="Swing_Credit" sheetId="8" r:id="rId8"/>
     <sheet name="Swing_Pass" sheetId="9" r:id="rId9"/>
     <sheet name="Events" sheetId="10" r:id="rId10"/>
+    <sheet name="Multisport" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Driving_Range!$A$1:$W$49</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="545">
   <si>
     <t>TC_ID</t>
   </si>
@@ -1604,6 +1605,78 @@
   </si>
   <si>
     <t>User can remove added player</t>
+  </si>
+  <si>
+    <t>SPORT_NAME</t>
+  </si>
+  <si>
+    <t>VENUE_NAME</t>
+  </si>
+  <si>
+    <t>TITLE_SCHEDULE</t>
+  </si>
+  <si>
+    <t>HOW_MUCH_SCHEDULE</t>
+  </si>
+  <si>
+    <t>TC_MLTS_001</t>
+  </si>
+  <si>
+    <t>Verify user can choose sport from sport option page</t>
+  </si>
+  <si>
+    <t>BILLIARD</t>
+  </si>
+  <si>
+    <t>TC_MLTS_002</t>
+  </si>
+  <si>
+    <t>Verify user can choose venue</t>
+  </si>
+  <si>
+    <t>BillWithPPD</t>
+  </si>
+  <si>
+    <t>TC_MLTS_003</t>
+  </si>
+  <si>
+    <t>Verify user can book venue</t>
+  </si>
+  <si>
+    <t>TC_MLTS_004</t>
+  </si>
+  <si>
+    <t>Verify user can select schedule</t>
+  </si>
+  <si>
+    <t>table1</t>
+  </si>
+  <si>
+    <t>TC_MLTS_005</t>
+  </si>
+  <si>
+    <t>Verify user can select add player</t>
+  </si>
+  <si>
+    <t>Joko</t>
+  </si>
+  <si>
+    <t>TC_MLTS_006</t>
+  </si>
+  <si>
+    <t>Verify user can remove player</t>
+  </si>
+  <si>
+    <t>TC_MLTS_007</t>
+  </si>
+  <si>
+    <t>Verify user can select payment</t>
+  </si>
+  <si>
+    <t>TC_MLTS_008</t>
+  </si>
+  <si>
+    <t>Verify user can book venue end to end until payment</t>
   </si>
 </sst>
 </file>
@@ -1616,7 +1689,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1632,11 +1705,6 @@
     <font>
       <sz val="10"/>
       <name val="Cambria"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2134,18 +2202,21 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2154,129 +2225,130 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2288,12 +2360,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2763,28 +2834,28 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:8">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2983,6 +3054,237 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:9">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:9">
+      <c r="A2" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:9">
+      <c r="A4" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="I5" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="I6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="I7" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="I8" t="s">
+        <v>520</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="14.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="47.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="27.2232142857143" customWidth="1"/>
+    <col min="4" max="4" width="14.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="18.0714285714286" customWidth="1"/>
+    <col min="6" max="6" width="24.5714285714286" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="20.0714285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="29" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2990,209 +3292,200 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="F1" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:9">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>492</v>
+        <v>526</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
-        <v>494</v>
-      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:9">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>499</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="G4" s="2" t="s">
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="I5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="I6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="I7" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="I8" t="s">
-        <v>520</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3223,61 +3516,61 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:19">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3641,2633 +3934,2633 @@
     <col min="18" max="18" width="20" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="21" width="20" style="10" customWidth="1"/>
-    <col min="23" max="23" width="70" style="10" customWidth="1"/>
+    <col min="21" max="21" width="20" style="2" customWidth="1"/>
+    <col min="23" max="23" width="70" style="2" customWidth="1"/>
     <col min="16380" max="16384" width="11.5267857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:23">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="6" t="s">
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="8" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5" t="s">
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="6" t="s">
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="8" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:23">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5" t="s">
+      <c r="I4" s="7"/>
+      <c r="J4" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="7">
         <v>3</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="6" t="s">
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="8" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
+      <c r="I5" s="7"/>
+      <c r="J5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="7">
         <v>2</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5" t="s">
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="6" t="s">
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="8" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
+      <c r="I6" s="7"/>
+      <c r="J6" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="7">
         <v>2</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5" t="s">
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="6" t="s">
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="7">
         <v>2</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5" t="s">
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="6" t="s">
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="s">
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="7">
         <v>2</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5" t="s">
+      <c r="N8" s="7"/>
+      <c r="O8" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="6" t="s">
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="7">
         <v>2</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5" t="s">
+      <c r="N9" s="7"/>
+      <c r="O9" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="6" t="s">
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="8" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" spans="1:23">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5" t="s">
+      <c r="I10" s="7"/>
+      <c r="J10" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="7">
         <v>2</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="N10" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="6" t="s">
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="8" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:23">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="7">
         <v>2</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="N11" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="6" t="s">
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="8" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
+      <c r="I12" s="7"/>
+      <c r="J12" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="7">
         <v>2</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5" t="s">
+      <c r="N12" s="7"/>
+      <c r="O12" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="6" t="s">
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="8" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="7">
         <v>2</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5" t="s">
+      <c r="N13" s="7"/>
+      <c r="O13" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="6" t="s">
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="8" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5" t="s">
+      <c r="I14" s="7"/>
+      <c r="J14" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="7">
         <v>2</v>
       </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5" t="s">
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="6" t="s">
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="8" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="7">
         <v>2</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5" t="s">
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="6" t="s">
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="8" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5" t="s">
+      <c r="I16" s="7"/>
+      <c r="J16" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="7">
         <v>2</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5" t="s">
+      <c r="N16" s="7"/>
+      <c r="O16" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="6" t="s">
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="8" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="7">
         <v>2</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="M17" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5" t="s">
+      <c r="N17" s="7"/>
+      <c r="O17" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="6" t="s">
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="8" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5" t="s">
+      <c r="I18" s="7"/>
+      <c r="J18" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="7">
         <v>2</v>
       </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5">
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7">
         <v>30</v>
       </c>
-      <c r="Q18" s="5" t="s">
+      <c r="Q18" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="R18" s="5" t="s">
+      <c r="R18" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="6" t="s">
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="8" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="7">
         <v>2</v>
       </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5">
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7">
         <v>30</v>
       </c>
-      <c r="Q19" s="5" t="s">
+      <c r="Q19" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="R19" s="5" t="s">
+      <c r="R19" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="6" t="s">
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="8" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5" t="s">
+      <c r="I20" s="7"/>
+      <c r="J20" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="7">
         <v>2</v>
       </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5" t="s">
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="T20" s="5" t="s">
+      <c r="T20" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="U20" s="7" t="s">
+      <c r="U20" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="V20" s="5" t="s">
+      <c r="V20" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="W20" s="6" t="s">
+      <c r="W20" s="8" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="7">
         <v>2</v>
       </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5" t="s">
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="T21" s="5" t="s">
+      <c r="T21" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="U21" s="7" t="s">
+      <c r="U21" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="V21" s="5" t="s">
+      <c r="V21" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="W21" s="6" t="s">
+      <c r="W21" s="8" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="6" t="s">
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="8" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="23" ht="33" customHeight="1" spans="1:23">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5" t="s">
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="6" t="s">
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="8" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5" t="s">
+      <c r="I24" s="7"/>
+      <c r="J24" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="K24" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L24" s="7">
         <v>3</v>
       </c>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="6" t="s">
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="8" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5" t="s">
+      <c r="I25" s="7"/>
+      <c r="J25" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K25" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L25" s="7">
         <v>2</v>
       </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5" t="s">
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="6" t="s">
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="8" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5" t="s">
+      <c r="I26" s="7"/>
+      <c r="J26" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K26" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="7">
         <v>2</v>
       </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5" t="s">
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="6" t="s">
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="J27" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K27" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="L27" s="5">
+      <c r="L27" s="7">
         <v>2</v>
       </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5" t="s">
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="6" t="s">
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5" t="s">
+      <c r="I28" s="7"/>
+      <c r="J28" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="K28" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L28" s="7">
         <v>2</v>
       </c>
-      <c r="M28" s="5" t="s">
+      <c r="M28" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5" t="s">
+      <c r="N28" s="7"/>
+      <c r="O28" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="6" t="s">
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="8" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="I29" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="J29" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="K29" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="L29" s="5">
+      <c r="L29" s="7">
         <v>2</v>
       </c>
-      <c r="M29" s="5" t="s">
+      <c r="M29" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5" t="s">
+      <c r="N29" s="7"/>
+      <c r="O29" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="5"/>
-      <c r="W29" s="6" t="s">
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="8" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="30" ht="33" customHeight="1" spans="1:23">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5" t="s">
+      <c r="I30" s="7"/>
+      <c r="J30" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="K30" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L30" s="5">
+      <c r="L30" s="7">
         <v>2</v>
       </c>
-      <c r="M30" s="5" t="s">
+      <c r="M30" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="N30" s="5" t="s">
+      <c r="N30" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="O30" s="5" t="s">
+      <c r="O30" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="5"/>
-      <c r="W30" s="6" t="s">
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="8" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="31" ht="33" customHeight="1" spans="1:23">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="I31" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K31" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="L31" s="5">
+      <c r="L31" s="7">
         <v>2</v>
       </c>
-      <c r="M31" s="5" t="s">
+      <c r="M31" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="N31" s="5" t="s">
+      <c r="N31" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="O31" s="5" t="s">
+      <c r="O31" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="5"/>
-      <c r="W31" s="6" t="s">
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="8" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="32" ht="33" customHeight="1" spans="1:23">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5" t="s">
+      <c r="I32" s="7"/>
+      <c r="J32" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K32" s="5" t="s">
+      <c r="K32" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L32" s="7">
         <v>2</v>
       </c>
-      <c r="M32" s="5" t="s">
+      <c r="M32" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5" t="s">
+      <c r="N32" s="7"/>
+      <c r="O32" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="7"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="6" t="s">
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="8" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="33" ht="33" customHeight="1" spans="1:23">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K33" s="5" t="s">
+      <c r="K33" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="L33" s="5">
+      <c r="L33" s="7">
         <v>2</v>
       </c>
-      <c r="M33" s="5" t="s">
+      <c r="M33" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5" t="s">
+      <c r="N33" s="7"/>
+      <c r="O33" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="5"/>
-      <c r="W33" s="6" t="s">
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="8" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5" t="s">
+      <c r="I34" s="7"/>
+      <c r="J34" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K34" s="5" t="s">
+      <c r="K34" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L34" s="5">
+      <c r="L34" s="7">
         <v>2</v>
       </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5" t="s">
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="5"/>
-      <c r="W34" s="6" t="s">
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="8" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K35" s="5" t="s">
+      <c r="K35" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="L35" s="5">
+      <c r="L35" s="7">
         <v>2</v>
       </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5" t="s">
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="5"/>
-      <c r="W35" s="6" t="s">
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="8" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5" t="s">
+      <c r="I36" s="7"/>
+      <c r="J36" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L36" s="5">
+      <c r="L36" s="7">
         <v>2</v>
       </c>
-      <c r="M36" s="5" t="s">
+      <c r="M36" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5" t="s">
+      <c r="N36" s="7"/>
+      <c r="O36" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
-      <c r="U36" s="7"/>
-      <c r="V36" s="5"/>
-      <c r="W36" s="6" t="s">
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="8" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="I37" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K37" s="5" t="s">
+      <c r="K37" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="L37" s="5">
+      <c r="L37" s="7">
         <v>2</v>
       </c>
-      <c r="M37" s="5" t="s">
+      <c r="M37" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5" t="s">
+      <c r="N37" s="7"/>
+      <c r="O37" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="5"/>
-      <c r="W37" s="6" t="s">
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="8" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="38" ht="33" customHeight="1" spans="1:23">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5" t="s">
+      <c r="I38" s="7"/>
+      <c r="J38" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K38" s="5" t="s">
+      <c r="K38" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="L38" s="5">
+      <c r="L38" s="7">
         <v>2</v>
       </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5" t="s">
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P38" s="5">
+      <c r="P38" s="7">
         <v>9</v>
       </c>
-      <c r="Q38" s="5" t="s">
+      <c r="Q38" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="R38" s="5" t="s">
+      <c r="R38" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
-      <c r="U38" s="7"/>
-      <c r="V38" s="5"/>
-      <c r="W38" s="6" t="s">
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="8" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="39" ht="33" customHeight="1" spans="1:23">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="I39" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J39" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K39" s="5" t="s">
+      <c r="K39" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="L39" s="5">
+      <c r="L39" s="7">
         <v>2</v>
       </c>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5" t="s">
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="P39" s="5">
+      <c r="P39" s="7">
         <v>9</v>
       </c>
-      <c r="Q39" s="5" t="s">
+      <c r="Q39" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="R39" s="5" t="s">
+      <c r="R39" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
-      <c r="U39" s="7"/>
-      <c r="V39" s="5"/>
-      <c r="W39" s="6" t="s">
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="8" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="40" ht="33" customHeight="1" spans="1:23">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5" t="s">
+      <c r="I40" s="7"/>
+      <c r="J40" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="K40" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L40" s="5">
+      <c r="L40" s="7">
         <v>2</v>
       </c>
-      <c r="M40" s="5" t="s">
+      <c r="M40" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5" t="s">
+      <c r="N40" s="7"/>
+      <c r="O40" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5" t="s">
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="T40" s="5" t="s">
+      <c r="T40" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="U40" s="7" t="s">
+      <c r="U40" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="V40" s="5" t="s">
+      <c r="V40" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="W40" s="6" t="s">
+      <c r="W40" s="8" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="41" ht="33" customHeight="1" spans="1:23">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="I41" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="J41" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K41" s="5" t="s">
+      <c r="K41" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L41" s="5">
+      <c r="L41" s="7">
         <v>2</v>
       </c>
-      <c r="M41" s="5" t="s">
+      <c r="M41" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5" t="s">
+      <c r="N41" s="7"/>
+      <c r="O41" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5" t="s">
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="T41" s="5" t="s">
+      <c r="T41" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="U41" s="7" t="s">
+      <c r="U41" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="V41" s="5" t="s">
+      <c r="V41" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="W41" s="6" t="s">
+      <c r="W41" s="8" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="I42" s="5" t="s">
+      <c r="I42" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K42" s="5" t="s">
+      <c r="K42" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L42" s="7">
         <v>2</v>
       </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5" t="s">
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="5"/>
-      <c r="W42" s="6" t="s">
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="9"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="8" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="I43" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J43" s="5" t="s">
+      <c r="J43" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K43" s="5" t="s">
+      <c r="K43" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="L43" s="5">
+      <c r="L43" s="7">
         <v>2</v>
       </c>
-      <c r="M43" s="5" t="s">
+      <c r="M43" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5" t="s">
+      <c r="N43" s="7"/>
+      <c r="O43" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="5"/>
-      <c r="W43" s="6" t="s">
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="8" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="44" ht="33" customHeight="1" spans="1:23">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="I44" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K44" s="5" t="s">
+      <c r="K44" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="L44" s="5">
+      <c r="L44" s="7">
         <v>2</v>
       </c>
-      <c r="M44" s="5" t="s">
+      <c r="M44" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="N44" s="5" t="s">
+      <c r="N44" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="O44" s="5" t="s">
+      <c r="O44" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="U44" s="7"/>
-      <c r="V44" s="5"/>
-      <c r="W44" s="6" t="s">
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="8" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="45" ht="33" customHeight="1" spans="1:23">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H45" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="I45" s="5" t="s">
+      <c r="I45" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J45" s="5" t="s">
+      <c r="J45" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="K45" s="5" t="s">
+      <c r="K45" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="L45" s="5">
+      <c r="L45" s="7">
         <v>2</v>
       </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5" t="s">
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5"/>
-      <c r="T45" s="5"/>
-      <c r="U45" s="7"/>
-      <c r="V45" s="5"/>
-      <c r="W45" s="6" t="s">
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="8" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="46" ht="33" customHeight="1" spans="1:23">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="I46" s="5" t="s">
+      <c r="I46" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J46" s="5" t="s">
+      <c r="J46" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K46" s="5" t="s">
+      <c r="K46" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="L46" s="5">
+      <c r="L46" s="7">
         <v>2</v>
       </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5" t="s">
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
-      <c r="U46" s="7"/>
-      <c r="V46" s="5"/>
-      <c r="W46" s="6" t="s">
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="8" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="47" ht="33" customHeight="1" spans="1:23">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="I47" s="5" t="s">
+      <c r="I47" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J47" s="5" t="s">
+      <c r="J47" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K47" s="5" t="s">
+      <c r="K47" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="L47" s="5">
+      <c r="L47" s="7">
         <v>2</v>
       </c>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5" t="s">
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5"/>
-      <c r="S47" s="5"/>
-      <c r="T47" s="5"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="5"/>
-      <c r="W47" s="6" t="s">
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="8" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="48" ht="33" customHeight="1" spans="1:23">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="H48" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="I48" s="5" t="s">
+      <c r="I48" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="J48" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="K48" s="5" t="s">
+      <c r="K48" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="L48" s="5">
+      <c r="L48" s="7">
         <v>2</v>
       </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5" t="s">
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
-      <c r="U48" s="7"/>
-      <c r="V48" s="5"/>
-      <c r="W48" s="6" t="s">
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
+      <c r="U48" s="9"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="8" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="49" ht="33" customHeight="1" spans="1:23">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="G49" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H49" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="I49" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J49" s="5" t="s">
+      <c r="J49" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="K49" s="5" t="s">
+      <c r="K49" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="L49" s="5">
+      <c r="L49" s="7">
         <v>2</v>
       </c>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5" t="s">
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="5"/>
-      <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
-      <c r="U49" s="7"/>
-      <c r="V49" s="5"/>
-      <c r="W49" s="6" t="s">
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
+      <c r="U49" s="9"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="8" t="s">
         <v>297</v>
       </c>
     </row>
@@ -6293,233 +6586,233 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6541,7 +6834,7 @@
       <c r="B23" t="s">
         <v>300</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="7">
         <v>5</v>
       </c>
     </row>
@@ -6560,7 +6853,7 @@
       <c r="A25" t="s">
         <v>223</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>302</v>
       </c>
       <c r="C25">
@@ -6574,7 +6867,7 @@
       <c r="B26" t="s">
         <v>300</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="7">
         <v>5</v>
       </c>
     </row>
@@ -6604,7 +6897,7 @@
       <c r="A29" t="s">
         <v>230</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="7" t="s">
         <v>302</v>
       </c>
       <c r="C29">
@@ -6629,7 +6922,7 @@
       <c r="B31" t="s">
         <v>300</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="7">
         <v>5</v>
       </c>
     </row>
@@ -6662,7 +6955,7 @@
       <c r="B34" t="s">
         <v>300</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="7">
         <v>5</v>
       </c>
     </row>
@@ -6681,7 +6974,7 @@
       <c r="A36" t="s">
         <v>241</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="7" t="s">
         <v>302</v>
       </c>
       <c r="C36">
@@ -6695,7 +6988,7 @@
       <c r="B37" t="s">
         <v>300</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="7">
         <v>5</v>
       </c>
     </row>
@@ -6703,7 +6996,7 @@
       <c r="A38" t="s">
         <v>247</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="7" t="s">
         <v>302</v>
       </c>
       <c r="C38">
@@ -6717,7 +7010,7 @@
       <c r="B39" t="s">
         <v>300</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="7">
         <v>5</v>
       </c>
     </row>
@@ -6736,7 +7029,7 @@
       <c r="A41" t="s">
         <v>253</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="7" t="s">
         <v>302</v>
       </c>
       <c r="C41">
@@ -6778,43 +7071,43 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:13">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -7656,31 +7949,31 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:9">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="11" t="s">
         <v>386</v>
       </c>
     </row>
@@ -8663,40 +8956,40 @@
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1" spans="1:4">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" ht="13.5" customHeight="1" spans="1:4">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1" spans="1:4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>414</v>
       </c>
     </row>
@@ -8738,820 +9031,820 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:18">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="6" t="s">
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="8" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A3" s="5">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="6" t="s">
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="8" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A4" s="5">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="6" t="s">
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="8" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A5" s="5">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5" t="s">
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="6" t="s">
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="8" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:18">
-      <c r="A6" s="5">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5" t="b">
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R6" s="6" t="s">
+      <c r="R6" s="8" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="7">
         <v>1</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5" t="b">
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="R7" s="8" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A8" s="5">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5" t="b">
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R8" s="6" t="s">
+      <c r="R8" s="8" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:18">
-      <c r="A9" s="5">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="6" t="s">
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="8" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A10" s="5">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="6" t="s">
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="8" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:18">
-      <c r="A11" s="5">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="6" t="s">
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="8" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A12" s="5">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5" t="s">
+      <c r="J12" s="7"/>
+      <c r="K12" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="7">
         <v>1</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5" t="b">
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R12" s="6" t="s">
+      <c r="R12" s="8" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A13" s="5">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5" t="s">
+      <c r="J13" s="7"/>
+      <c r="K13" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="7">
         <v>1</v>
       </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5" t="b">
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R13" s="6" t="s">
+      <c r="R13" s="8" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A14" s="5">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5" t="s">
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="6" t="s">
+      <c r="Q14" s="7"/>
+      <c r="R14" s="8" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A15" s="5">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5" t="s">
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="6" t="s">
+      <c r="Q15" s="7"/>
+      <c r="R15" s="8" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:18">
-      <c r="A16" s="5">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5" t="s">
+      <c r="J16" s="7"/>
+      <c r="K16" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="7">
         <v>1</v>
       </c>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5" t="s">
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="Q16" s="5" t="b">
+      <c r="Q16" s="7" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R16" s="6" t="s">
+      <c r="R16" s="8" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:18">
-      <c r="A17" s="5">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5" t="s">
+      <c r="J17" s="7"/>
+      <c r="K17" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="7">
         <v>1</v>
       </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5" t="s">
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="Q17" s="5" t="b">
+      <c r="Q17" s="7" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R17" s="6" t="s">
+      <c r="R17" s="8" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A18" s="5">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5" t="s">
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="6" t="s">
+      <c r="Q18" s="7"/>
+      <c r="R18" s="8" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A19" s="5">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5" t="s">
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5" t="b">
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R19" s="6" t="s">
+      <c r="R19" s="8" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:18">
-      <c r="A20" s="5">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="6" t="s">
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="8" t="s">
         <v>486</v>
       </c>
     </row>
